--- a/docs/Decodifiche/12_dec_tipo_consenso.xlsx
+++ b/docs/Decodifiche/12_dec_tipo_consenso.xlsx
@@ -62,7 +62,7 @@
     <t>4</t>
   </si>
   <si>
-    <t>Sentenza del tribunale dopo rifiuto consenso materno</t>
+    <t>Sentenza del tribunale dopo rifiuto consenso</t>
   </si>
 </sst>
 </file>
